--- a/نادي البناء.xlsx
+++ b/نادي البناء.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="300" windowWidth="18495" windowHeight="11700" activeTab="2"/>
+    <workbookView xWindow="480" yWindow="300" windowWidth="18495" windowHeight="11700"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="51">
   <si>
     <t>الاسم</t>
   </si>
@@ -128,12 +128,57 @@
   <si>
     <t>TOTAL</t>
   </si>
+  <si>
+    <t>سعدنا\ محمد \ سيداحمد العالم</t>
+  </si>
+  <si>
+    <t>213 553646697</t>
+  </si>
+  <si>
+    <t>سعدن \ محمد \ سيداحمد العالم</t>
+  </si>
+  <si>
+    <t>التاريخ</t>
+  </si>
+  <si>
+    <t>فاعلة خير</t>
+  </si>
+  <si>
+    <t>تبرع</t>
+  </si>
+  <si>
+    <t>سيهام \ حمودي</t>
+  </si>
+  <si>
+    <t>متش لعيون</t>
+  </si>
+  <si>
+    <t>افطار الصائم</t>
+  </si>
+  <si>
+    <t>جائزة متش لعيون</t>
+  </si>
+  <si>
+    <t>التبرع</t>
+  </si>
+  <si>
+    <t>المصاريف</t>
+  </si>
+  <si>
+    <t>المجموع</t>
+  </si>
+  <si>
+    <t>التفاصيل</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="12">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -213,6 +258,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -222,7 +281,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -274,15 +333,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -365,12 +440,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -383,11 +452,44 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -395,17 +497,41 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
+    <cellStyle name="Milliers" xfId="2" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="23">
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -442,6 +568,20 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -456,7 +596,7 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
         <color theme="1"/>
-        <name val="Microsoft YaHei UI"/>
+        <name val="Microsoft YaHei"/>
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
@@ -478,6 +618,105 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Microsoft YaHei UI"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Microsoft YaHei"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Microsoft YaHei UI"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -588,7 +827,7 @@
         <name val="Microsoft YaHei UI"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -678,15 +917,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>723900</xdr:colOff>
-      <xdr:row>131</xdr:row>
+      <xdr:row>129</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>132</xdr:row>
+      <xdr:row>130</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -813,43 +1052,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Tableau5" displayName="Tableau5" ref="D5:F23" totalsRowShown="0">
-  <autoFilter ref="D5:F23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Tableau5" displayName="Tableau5" ref="H3:J22" totalsRowShown="0">
+  <autoFilter ref="H3:J22"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="الرقم" dataDxfId="17"/>
-    <tableColumn id="2" name="الاسم" dataDxfId="16"/>
-    <tableColumn id="3" name="العدد" dataDxfId="15"/>
+    <tableColumn id="1" name="الرقم" dataDxfId="22"/>
+    <tableColumn id="2" name="الاسم" dataDxfId="21"/>
+    <tableColumn id="3" name="العدد" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tableau24" displayName="Tableau24" ref="C5:H31" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tableau24" displayName="Tableau24" ref="C5:H31" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <autoFilter ref="C5:H31"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="طرق الدفع" dataDxfId="12"/>
-    <tableColumn id="2" name="تاريخ الدفع" dataDxfId="11"/>
-    <tableColumn id="3" name="المبلغ" dataDxfId="10"/>
-    <tableColumn id="4" name="الرقم" dataDxfId="9"/>
-    <tableColumn id="5" name="الاسم" dataDxfId="8"/>
-    <tableColumn id="6" name="العدد" dataDxfId="7"/>
+    <tableColumn id="1" name="طرق الدفع" dataDxfId="17"/>
+    <tableColumn id="2" name="تاريخ الدفع" dataDxfId="16"/>
+    <tableColumn id="3" name="المبلغ" dataDxfId="15"/>
+    <tableColumn id="4" name="الرقم" dataDxfId="14"/>
+    <tableColumn id="5" name="الاسم" dataDxfId="13"/>
+    <tableColumn id="6" name="العدد" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tableau242" displayName="Tableau242" ref="C5:G26" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="C5:G26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tableau242" displayName="Tableau242" ref="C6:G26" headerRowCount="0" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <tableColumns count="5">
-    <tableColumn id="1" name="طرق الدفع" dataDxfId="4"/>
-    <tableColumn id="2" name="تاريخ الدفع" dataDxfId="3"/>
-    <tableColumn id="3" name="المبلغ" dataDxfId="2"/>
-    <tableColumn id="5" name="الاسم" dataDxfId="1"/>
-    <tableColumn id="6" name="العدد" dataDxfId="0"/>
+    <tableColumn id="1" name="طرق الدفع" headerRowDxfId="9" dataDxfId="8"/>
+    <tableColumn id="2" name="تاريخ الدفع" headerRowDxfId="7" dataDxfId="6"/>
+    <tableColumn id="3" name="المبلغ" headerRowDxfId="5" dataDxfId="4"/>
+    <tableColumn id="5" name="الاسم" headerRowDxfId="3" dataDxfId="2"/>
+    <tableColumn id="6" name="العدد" headerRowDxfId="1" dataDxfId="0"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1138,1171 +1376,1344 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A3:J149"/>
+  <dimension ref="B1:S147"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="1"/>
-    <col min="2" max="2" width="10.5703125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="2"/>
-    <col min="4" max="4" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8" style="2" customWidth="1"/>
-    <col min="7" max="8" width="11.42578125" style="1"/>
-    <col min="9" max="9" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.42578125" style="1"/>
+    <col min="1" max="5" width="11.42578125" style="1"/>
+    <col min="6" max="6" width="10.5703125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="2"/>
+    <col min="8" max="8" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8" style="2" customWidth="1"/>
+    <col min="11" max="12" width="11.42578125" style="1"/>
+    <col min="13" max="13" width="9.28515625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="1"/>
+    <col min="16" max="16" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:10" ht="15" customHeight="1">
-      <c r="C3" s="12"/>
-      <c r="D3" s="36" t="s">
+    <row r="1" spans="2:19" ht="15" customHeight="1">
+      <c r="G1" s="12"/>
+      <c r="H1" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-    </row>
-    <row r="4" spans="1:10" ht="15" customHeight="1">
-      <c r="C4" s="12"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="1:10" ht="16.5">
-      <c r="A5" s="1">
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+    </row>
+    <row r="2" spans="2:19" ht="15" customHeight="1">
+      <c r="G2" s="12"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+    </row>
+    <row r="3" spans="2:19" ht="16.5">
+      <c r="B3" s="1">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2</v>
+      </c>
+      <c r="E3" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="24">
+      <c r="F3" s="24">
         <v>12</v>
       </c>
-      <c r="C5" s="2">
+      <c r="G3" s="2">
         <v>11</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-    </row>
-    <row r="6" spans="1:10" ht="16.5">
-      <c r="B6" s="4">
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+    </row>
+    <row r="4" spans="2:19" ht="16.5">
+      <c r="E4" s="1">
         <v>50</v>
       </c>
-      <c r="C6" s="2">
+      <c r="F4" s="4">
         <v>50</v>
       </c>
-      <c r="D6" s="4">
+      <c r="G4" s="2">
+        <v>50</v>
+      </c>
+      <c r="H4" s="4">
         <v>49653246</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="1">
+      <c r="J4" s="1">
         <v>1</v>
       </c>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-    </row>
-    <row r="7" spans="1:10" ht="15.75" customHeight="1">
-      <c r="B7" s="4"/>
-      <c r="C7" s="4">
-        <v>200</v>
-      </c>
-      <c r="D7" s="4">
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29"/>
+    </row>
+    <row r="5" spans="2:19" ht="15.75" customHeight="1">
+      <c r="B5" s="1">
+        <v>50</v>
+      </c>
+      <c r="C5" s="1">
+        <v>50</v>
+      </c>
+      <c r="D5" s="4">
+        <v>50</v>
+      </c>
+      <c r="E5" s="4">
+        <v>50</v>
+      </c>
+      <c r="F5" s="4">
+        <v>50</v>
+      </c>
+      <c r="G5" s="4">
+        <v>50</v>
+      </c>
+      <c r="H5" s="4">
         <v>37695464</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="I5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="1">
+      <c r="J5" s="1">
         <v>2</v>
       </c>
-      <c r="G7" s="31"/>
-      <c r="H7" s="32" t="s">
+      <c r="K5" s="29"/>
+      <c r="L5" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="31">
-        <f>SUM(I8:I11)</f>
-        <v>2600</v>
-      </c>
-      <c r="J7" s="32"/>
-    </row>
-    <row r="8" spans="1:10" ht="20.25" customHeight="1">
-      <c r="B8" s="9">
+      <c r="M5" s="29">
+        <f>SUM(M6:M26)</f>
+        <v>710</v>
+      </c>
+      <c r="N5" s="30"/>
+    </row>
+    <row r="6" spans="2:19" ht="20.25" customHeight="1">
+      <c r="C6" s="1">
         <v>50</v>
       </c>
-      <c r="C8" s="4">
+      <c r="E6" s="9">
         <v>50</v>
       </c>
-      <c r="D8" s="4">
+      <c r="G6" s="4">
+        <v>50</v>
+      </c>
+      <c r="H6" s="4">
         <v>31155428</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="I6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="1">
+      <c r="J6" s="1">
         <v>3</v>
       </c>
-      <c r="G8" s="31"/>
-      <c r="H8" s="20">
+      <c r="K6" s="29"/>
+      <c r="L6" s="20">
         <v>45962</v>
       </c>
-      <c r="I8" s="31">
+      <c r="M6" s="29">
         <v>2100</v>
       </c>
-      <c r="J8" s="31"/>
-    </row>
-    <row r="9" spans="1:10" ht="16.5" customHeight="1">
-      <c r="B9" s="4"/>
-      <c r="C9" s="4">
+      <c r="N6" s="29"/>
+    </row>
+    <row r="7" spans="2:19" ht="16.5" customHeight="1">
+      <c r="E7" s="4">
         <v>50</v>
       </c>
+      <c r="F7" s="4">
+        <v>50</v>
+      </c>
+      <c r="G7" s="4">
+        <v>50</v>
+      </c>
+      <c r="H7" s="4">
+        <v>33054678</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="1">
+        <v>4</v>
+      </c>
+      <c r="K7" s="29"/>
+      <c r="L7" s="20">
+        <v>45992</v>
+      </c>
+      <c r="M7" s="29">
+        <v>500</v>
+      </c>
+      <c r="N7" s="31"/>
+    </row>
+    <row r="8" spans="2:19" ht="16.5" customHeight="1">
+      <c r="F8" s="4">
+        <v>50</v>
+      </c>
+      <c r="G8" s="4">
+        <v>50</v>
+      </c>
+      <c r="H8" s="4">
+        <v>32900026</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" s="1">
+        <v>5</v>
+      </c>
+      <c r="K8" s="29"/>
+      <c r="L8" s="20">
+        <v>46023</v>
+      </c>
+      <c r="M8" s="29">
+        <v>650</v>
+      </c>
+      <c r="N8" s="32"/>
+    </row>
+    <row r="9" spans="2:19" ht="16.5" customHeight="1">
       <c r="D9" s="4">
-        <v>33054678</v>
-      </c>
-      <c r="E9" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="4">
+        <v>50</v>
+      </c>
+      <c r="F9" s="4">
+        <v>50</v>
+      </c>
+      <c r="G9" s="4">
+        <v>50</v>
+      </c>
+      <c r="H9" s="4">
+        <v>26048274</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="1">
+        <v>6</v>
+      </c>
+      <c r="K9" s="29"/>
+      <c r="L9" s="20">
+        <v>46054</v>
+      </c>
+      <c r="M9" s="29">
+        <v>1460</v>
+      </c>
+      <c r="N9" s="32"/>
+    </row>
+    <row r="10" spans="2:19" ht="16.5" customHeight="1">
+      <c r="D10" s="1">
+        <v>50</v>
+      </c>
+      <c r="F10" s="4">
+        <v>50</v>
+      </c>
+      <c r="G10" s="4">
+        <v>50</v>
+      </c>
+      <c r="H10" s="4">
+        <v>31114426</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="1">
+        <v>7</v>
+      </c>
+      <c r="K10" s="29"/>
+      <c r="L10" s="20">
+        <v>46088</v>
+      </c>
+      <c r="M10" s="31">
+        <v>-500</v>
+      </c>
+      <c r="N10" s="32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" ht="16.5">
+      <c r="F11" s="4">
+        <v>50</v>
+      </c>
+      <c r="G11" s="4">
+        <v>50</v>
+      </c>
+      <c r="H11" s="4"/>
+      <c r="I11" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="1">
+        <v>8</v>
+      </c>
+      <c r="K11" s="2"/>
+      <c r="L11" s="20">
+        <v>46092</v>
+      </c>
+      <c r="M11" s="44">
+        <v>-3000</v>
+      </c>
+      <c r="N11" s="28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19" ht="16.5">
+      <c r="E12" s="1">
+        <v>50</v>
+      </c>
+      <c r="F12" s="4">
+        <v>50</v>
+      </c>
+      <c r="G12" s="4">
+        <v>50</v>
+      </c>
+      <c r="H12" s="4">
+        <v>48285050</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="1">
         <v>9</v>
       </c>
-      <c r="F9" s="1">
-        <v>4</v>
-      </c>
-      <c r="G9" s="31"/>
-      <c r="H9" s="20">
+      <c r="K12" s="2"/>
+      <c r="L12" s="20">
+        <v>46092</v>
+      </c>
+      <c r="M12" s="49">
+        <v>-500</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" ht="16.5">
+      <c r="F13" s="4"/>
+      <c r="G13" s="4">
+        <v>50</v>
+      </c>
+      <c r="H13" s="4">
+        <v>22160032724</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="1">
+        <v>10</v>
+      </c>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+    </row>
+    <row r="14" spans="2:19" ht="16.5">
+      <c r="F14" s="4"/>
+      <c r="G14" s="4">
+        <v>50</v>
+      </c>
+      <c r="H14" s="4">
+        <v>32232227</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="1">
+        <v>11</v>
+      </c>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="P14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19" ht="16.5">
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4">
+        <v>36281129</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="1">
+        <v>12</v>
+      </c>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="R15" s="29">
+        <v>2100</v>
+      </c>
+      <c r="S15" s="20">
+        <v>45962</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19" ht="16.5">
+      <c r="F16" s="4">
+        <v>50</v>
+      </c>
+      <c r="G16" s="4">
+        <v>50</v>
+      </c>
+      <c r="H16" s="4"/>
+      <c r="I16" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" s="1">
+        <v>13</v>
+      </c>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="R16" s="29">
+        <v>500</v>
+      </c>
+      <c r="S16" s="20">
         <v>45992</v>
       </c>
-      <c r="I9" s="31">
+    </row>
+    <row r="17" spans="4:19" ht="16.5">
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4">
+        <v>34396660</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="1">
+        <v>14</v>
+      </c>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="R17" s="29">
+        <v>650</v>
+      </c>
+      <c r="S17" s="20">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="18" spans="4:19" ht="16.5">
+      <c r="E18" s="1">
+        <v>50</v>
+      </c>
+      <c r="F18" s="4">
+        <v>50</v>
+      </c>
+      <c r="G18" s="4">
+        <v>50</v>
+      </c>
+      <c r="H18" s="4">
+        <v>26855949</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="1">
+        <v>15</v>
+      </c>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="R18" s="29">
+        <v>1460</v>
+      </c>
+      <c r="S18" s="20">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="19" spans="4:19" ht="16.5">
+      <c r="F19" s="4"/>
+      <c r="G19" s="4">
+        <v>50</v>
+      </c>
+      <c r="H19" s="4">
+        <v>20794925</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="J19" s="1">
+        <v>16</v>
+      </c>
+      <c r="P19" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q19" s="31">
         <v>500</v>
       </c>
-      <c r="J9" s="33"/>
-    </row>
-    <row r="10" spans="1:10" ht="16.5" customHeight="1">
-      <c r="B10" s="4">
+      <c r="S19" s="20">
+        <v>46088</v>
+      </c>
+    </row>
+    <row r="20" spans="4:19" ht="16.5">
+      <c r="E20" s="1">
         <v>50</v>
       </c>
-      <c r="C10" s="4">
+      <c r="F20" s="4"/>
+      <c r="G20" s="4">
         <v>50</v>
       </c>
-      <c r="D10" s="4">
-        <v>32900026</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="1">
-        <v>5</v>
-      </c>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="35"/>
-    </row>
-    <row r="11" spans="1:10" ht="16.5" customHeight="1">
-      <c r="B11" s="4">
+      <c r="H20" s="4">
+        <v>37246160</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J20" s="1">
+        <v>17</v>
+      </c>
+      <c r="P20" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q20" s="44">
+        <v>3000</v>
+      </c>
+      <c r="S20" s="20">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="21" spans="4:19" ht="16.5">
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="10">
+        <v>38301688</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J21" s="2">
+        <v>18</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q21" s="49">
+        <v>500</v>
+      </c>
+      <c r="S21" s="20">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="22" spans="4:19" ht="33">
+      <c r="D22" s="4">
         <v>50</v>
       </c>
-      <c r="C11" s="4">
+      <c r="E22" s="4">
         <v>50</v>
       </c>
-      <c r="D11" s="4">
-        <v>26048274</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="1">
-        <v>6</v>
-      </c>
-      <c r="G11" s="31"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="35"/>
-    </row>
-    <row r="12" spans="1:10" ht="16.5" customHeight="1">
-      <c r="B12" s="4">
+      <c r="F22" s="4">
         <v>50</v>
       </c>
-      <c r="C12" s="4">
+      <c r="G22" s="4">
         <v>50</v>
       </c>
-      <c r="D12" s="4">
-        <v>31114426</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="1">
-        <v>7</v>
-      </c>
-      <c r="G12" s="31"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="35"/>
-    </row>
-    <row r="13" spans="1:10" ht="16.5">
-      <c r="B13" s="4">
-        <v>50</v>
-      </c>
-      <c r="C13" s="4">
-        <v>50</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="1">
-        <v>8</v>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="30"/>
-    </row>
-    <row r="14" spans="1:10" ht="16.5">
-      <c r="B14" s="4">
-        <v>50</v>
-      </c>
-      <c r="C14" s="4">
-        <v>50</v>
-      </c>
-      <c r="D14" s="4">
-        <v>48285050</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="1">
-        <v>9</v>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" ht="16.5">
-      <c r="B15" s="4"/>
-      <c r="C15" s="4">
-        <v>50</v>
-      </c>
-      <c r="D15" s="4">
-        <v>22160032724</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="1">
-        <v>10</v>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" ht="16.5">
-      <c r="B16" s="4"/>
-      <c r="C16" s="4">
-        <v>50</v>
-      </c>
-      <c r="D16" s="4">
-        <v>32232227</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="1">
-        <v>11</v>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-    </row>
-    <row r="17" spans="2:10" ht="16.5">
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4">
-        <v>36281129</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="1">
-        <v>12</v>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-    </row>
-    <row r="18" spans="2:10" ht="16.5">
-      <c r="B18" s="4">
-        <v>50</v>
-      </c>
-      <c r="C18" s="4">
-        <v>50</v>
-      </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" s="1">
-        <v>13</v>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-    </row>
-    <row r="19" spans="2:10" ht="16.5">
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4">
-        <v>34396660</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" s="1">
-        <v>14</v>
-      </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-    </row>
-    <row r="20" spans="2:10" ht="16.5">
-      <c r="B20" s="4">
-        <v>50</v>
-      </c>
-      <c r="C20" s="4">
-        <v>100</v>
-      </c>
-      <c r="D20" s="4">
-        <v>26855949</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="1">
-        <v>15</v>
-      </c>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-    </row>
-    <row r="21" spans="2:10" ht="16.5">
-      <c r="B21" s="4"/>
-      <c r="C21" s="4">
-        <v>50</v>
-      </c>
-      <c r="D21" s="4">
-        <v>20794925</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F21" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10" ht="16.5">
-      <c r="B22" s="4">
-        <v>50</v>
-      </c>
-      <c r="C22" s="4">
-        <v>50</v>
-      </c>
-      <c r="D22" s="4">
-        <v>37246160</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10" ht="16.5">
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="10">
-        <v>38301688</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F23" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" ht="16.5">
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-    </row>
-    <row r="25" spans="2:10" ht="16.5">
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-    </row>
-    <row r="26" spans="2:10" ht="16.5">
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-    </row>
-    <row r="27" spans="2:10" ht="16.5">
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-    </row>
-    <row r="28" spans="2:10" ht="16.5">
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-    </row>
-    <row r="29" spans="2:10" ht="16.5">
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-    </row>
-    <row r="30" spans="2:10" ht="16.5">
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-    </row>
-    <row r="31" spans="2:10" ht="16.5">
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-    </row>
-    <row r="32" spans="2:10" ht="16.5">
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-    </row>
-    <row r="33" spans="2:5" ht="16.5">
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-    </row>
-    <row r="34" spans="2:5" ht="16.5">
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-    </row>
-    <row r="35" spans="2:5" ht="16.5">
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-    </row>
-    <row r="36" spans="2:5" ht="16.5">
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-    </row>
-    <row r="37" spans="2:5" ht="16.5">
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-    </row>
-    <row r="38" spans="2:5" ht="16.5">
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-    </row>
-    <row r="39" spans="2:5" ht="16.5">
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-    </row>
-    <row r="40" spans="2:5" ht="16.5">
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-    </row>
-    <row r="41" spans="2:5" ht="16.5">
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-    </row>
-    <row r="42" spans="2:5" ht="16.5">
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-    </row>
-    <row r="43" spans="2:5" ht="16.5">
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-    </row>
-    <row r="44" spans="2:5" ht="16.5">
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-    </row>
-    <row r="45" spans="2:5" ht="16.5">
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-    </row>
-    <row r="46" spans="2:5" ht="16.5">
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-    </row>
-    <row r="47" spans="2:5" ht="16.5">
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-    </row>
-    <row r="48" spans="2:5" ht="16.5">
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-    </row>
-    <row r="49" spans="2:5" ht="16.5">
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-    </row>
-    <row r="50" spans="2:5" ht="16.5">
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-    </row>
-    <row r="51" spans="2:5" ht="16.5">
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-    </row>
-    <row r="52" spans="2:5" ht="16.5">
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-    </row>
-    <row r="53" spans="2:5" ht="16.5">
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-    </row>
-    <row r="54" spans="2:5" ht="16.5">
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-    </row>
-    <row r="55" spans="2:5" ht="16.5">
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-    </row>
-    <row r="56" spans="2:5" ht="16.5">
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-    </row>
-    <row r="57" spans="2:5" ht="16.5">
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-    </row>
-    <row r="58" spans="2:5" ht="16.5">
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-    </row>
-    <row r="59" spans="2:5" ht="16.5">
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-    </row>
-    <row r="60" spans="2:5" ht="16.5">
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-    </row>
-    <row r="61" spans="2:5" ht="16.5">
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
-    </row>
-    <row r="62" spans="2:5" ht="16.5">
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-    </row>
-    <row r="63" spans="2:5" ht="16.5">
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-    </row>
-    <row r="64" spans="2:5" ht="16.5">
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-    </row>
-    <row r="65" spans="2:5" ht="16.5">
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-    </row>
-    <row r="66" spans="2:5" ht="16.5">
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-    </row>
-    <row r="67" spans="2:5" ht="16.5">
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-    </row>
-    <row r="68" spans="2:5" ht="16.5">
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-    </row>
-    <row r="69" spans="2:5" ht="16.5">
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-    </row>
-    <row r="70" spans="2:5" ht="16.5">
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-    </row>
-    <row r="71" spans="2:5" ht="16.5">
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
-    </row>
-    <row r="72" spans="2:5" ht="16.5">
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-    </row>
-    <row r="73" spans="2:5" ht="16.5">
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-    </row>
-    <row r="74" spans="2:5" ht="16.5">
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-    </row>
-    <row r="75" spans="2:5" ht="16.5">
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
-    </row>
-    <row r="76" spans="2:5" ht="16.5">
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-    </row>
-    <row r="77" spans="2:5" ht="16.5">
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-    </row>
-    <row r="78" spans="2:5" ht="16.5">
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-    </row>
-    <row r="79" spans="2:5" ht="16.5">
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-    </row>
-    <row r="80" spans="2:5" ht="16.5">
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-    </row>
-    <row r="81" spans="2:5" ht="16.5">
-      <c r="B81" s="4"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
-    </row>
-    <row r="82" spans="2:5" ht="16.5">
-      <c r="B82" s="4"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
-    </row>
-    <row r="83" spans="2:5" ht="16.5">
-      <c r="B83" s="4"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="4"/>
-    </row>
-    <row r="84" spans="2:5" ht="16.5">
-      <c r="B84" s="4"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
-    </row>
-    <row r="85" spans="2:5" ht="16.5">
-      <c r="B85" s="4"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
-    </row>
-    <row r="86" spans="2:5" ht="16.5">
-      <c r="B86" s="4"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-    </row>
-    <row r="87" spans="2:5" ht="16.5">
-      <c r="B87" s="4"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
-    </row>
-    <row r="88" spans="2:5" ht="16.5">
-      <c r="B88" s="4"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-    </row>
-    <row r="89" spans="2:5" ht="16.5">
-      <c r="B89" s="4"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
-    </row>
-    <row r="90" spans="2:5" ht="16.5">
-      <c r="B90" s="4"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
-    </row>
-    <row r="91" spans="2:5" ht="16.5">
-      <c r="B91" s="4"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="4"/>
-    </row>
-    <row r="92" spans="2:5" ht="16.5">
-      <c r="B92" s="4"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
-    </row>
-    <row r="93" spans="2:5" ht="16.5">
-      <c r="B93" s="4"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
-      <c r="E93" s="4"/>
-    </row>
-    <row r="94" spans="2:5" ht="16.5">
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
-    </row>
-    <row r="95" spans="2:5" ht="16.5">
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-    </row>
-    <row r="96" spans="2:5" ht="16.5">
-      <c r="B96" s="4"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
-      <c r="E96" s="4"/>
-    </row>
-    <row r="97" spans="2:5" ht="16.5">
-      <c r="B97" s="4"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="4"/>
-      <c r="E97" s="4"/>
-    </row>
-    <row r="98" spans="2:5" ht="16.5">
-      <c r="B98" s="4"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="4"/>
-      <c r="E98" s="4"/>
-    </row>
-    <row r="99" spans="2:5" ht="16.5">
-      <c r="B99" s="4"/>
-      <c r="C99" s="4"/>
-      <c r="D99" s="4"/>
-      <c r="E99" s="4"/>
-    </row>
-    <row r="100" spans="2:5" ht="16.5">
-      <c r="B100" s="4"/>
-      <c r="C100" s="4"/>
-      <c r="D100" s="4"/>
-      <c r="E100" s="4"/>
-    </row>
-    <row r="101" spans="2:5" ht="16.5">
-      <c r="B101" s="4"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="4"/>
-      <c r="E101" s="4"/>
-    </row>
-    <row r="102" spans="2:5" ht="16.5">
-      <c r="B102" s="4"/>
-      <c r="C102" s="4"/>
-      <c r="D102" s="4"/>
-      <c r="E102" s="4"/>
-    </row>
-    <row r="103" spans="2:5" ht="16.5">
-      <c r="B103" s="4"/>
-      <c r="C103" s="4"/>
-      <c r="D103" s="4"/>
-      <c r="E103" s="4"/>
-    </row>
-    <row r="104" spans="2:5" ht="16.5">
-      <c r="B104" s="4"/>
-      <c r="C104" s="4"/>
-      <c r="D104" s="4"/>
-      <c r="E104" s="4"/>
-    </row>
-    <row r="105" spans="2:5" ht="16.5">
-      <c r="B105" s="4"/>
-      <c r="C105" s="4"/>
-      <c r="D105" s="4"/>
-      <c r="E105" s="4"/>
-    </row>
-    <row r="106" spans="2:5" ht="16.5">
-      <c r="B106" s="4"/>
-      <c r="C106" s="4"/>
-      <c r="D106" s="4"/>
-      <c r="E106" s="4"/>
-    </row>
-    <row r="107" spans="2:5" ht="16.5">
-      <c r="B107" s="4"/>
-      <c r="C107" s="4"/>
-      <c r="D107" s="4"/>
-      <c r="E107" s="4"/>
-    </row>
-    <row r="108" spans="2:5" ht="16.5">
-      <c r="B108" s="4"/>
-      <c r="C108" s="4"/>
-      <c r="D108" s="4"/>
-      <c r="E108" s="4"/>
-    </row>
-    <row r="109" spans="2:5" ht="16.5">
-      <c r="B109" s="4"/>
-      <c r="C109" s="4"/>
-      <c r="D109" s="4"/>
-      <c r="E109" s="4"/>
-    </row>
-    <row r="110" spans="2:5" ht="16.5">
-      <c r="B110" s="4"/>
-      <c r="C110" s="4"/>
-      <c r="D110" s="4"/>
-      <c r="E110" s="4"/>
-    </row>
-    <row r="111" spans="2:5" ht="16.5">
-      <c r="B111" s="4"/>
-      <c r="C111" s="4"/>
-      <c r="D111" s="4"/>
-      <c r="E111" s="4"/>
-    </row>
-    <row r="112" spans="2:5" ht="16.5">
-      <c r="B112" s="4"/>
-      <c r="C112" s="4"/>
-      <c r="D112" s="4"/>
-      <c r="E112" s="4"/>
-    </row>
-    <row r="113" spans="2:5" ht="16.5">
-      <c r="B113" s="4"/>
-      <c r="C113" s="4"/>
-      <c r="D113" s="4"/>
-      <c r="E113" s="4"/>
-    </row>
-    <row r="114" spans="2:5" ht="16.5">
-      <c r="B114" s="4"/>
-      <c r="C114" s="4"/>
-      <c r="D114" s="4"/>
-      <c r="E114" s="4"/>
-    </row>
-    <row r="115" spans="2:5" ht="16.5">
-      <c r="B115" s="4"/>
-      <c r="C115" s="4"/>
-      <c r="D115" s="4"/>
-      <c r="E115" s="4"/>
-    </row>
-    <row r="116" spans="2:5" ht="16.5">
-      <c r="B116" s="4"/>
-      <c r="C116" s="4"/>
-      <c r="D116" s="4"/>
-      <c r="E116" s="4"/>
-    </row>
-    <row r="117" spans="2:5" ht="16.5">
-      <c r="B117" s="4"/>
-      <c r="C117" s="4"/>
-      <c r="D117" s="4"/>
-      <c r="E117" s="4"/>
-    </row>
-    <row r="118" spans="2:5" ht="16.5">
-      <c r="B118" s="4"/>
-      <c r="C118" s="4"/>
-      <c r="D118" s="4"/>
-      <c r="E118" s="4"/>
-    </row>
-    <row r="119" spans="2:5" ht="16.5">
-      <c r="B119" s="4"/>
-      <c r="C119" s="4"/>
-      <c r="D119" s="4"/>
-      <c r="E119" s="4"/>
-    </row>
-    <row r="120" spans="2:5" ht="16.5">
-      <c r="B120" s="4"/>
-      <c r="C120" s="4"/>
-      <c r="D120" s="4"/>
-      <c r="E120" s="4"/>
-    </row>
-    <row r="121" spans="2:5" ht="16.5">
-      <c r="B121" s="4"/>
-      <c r="C121" s="4"/>
-      <c r="D121" s="4"/>
-      <c r="E121" s="4"/>
-    </row>
-    <row r="122" spans="2:5" ht="16.5">
-      <c r="B122" s="4"/>
-      <c r="C122" s="4"/>
-      <c r="D122" s="4"/>
-      <c r="E122" s="4"/>
-    </row>
-    <row r="123" spans="2:5" ht="16.5">
-      <c r="B123" s="4"/>
-      <c r="C123" s="4"/>
-      <c r="D123" s="4"/>
-      <c r="E123" s="4"/>
-    </row>
-    <row r="124" spans="2:5" ht="16.5">
-      <c r="B124" s="4"/>
-      <c r="C124" s="4"/>
-      <c r="D124" s="4"/>
-      <c r="E124" s="4"/>
-    </row>
-    <row r="125" spans="2:5" ht="16.5">
-      <c r="B125" s="4"/>
-      <c r="C125" s="4"/>
-      <c r="D125" s="4"/>
-      <c r="E125" s="4"/>
-    </row>
-    <row r="126" spans="2:5" ht="16.5">
-      <c r="B126" s="4"/>
-      <c r="C126" s="4"/>
-      <c r="D126" s="4"/>
-      <c r="E126" s="4"/>
-    </row>
-    <row r="127" spans="2:5" ht="16.5">
-      <c r="B127" s="4"/>
-      <c r="C127" s="4"/>
-      <c r="D127" s="4"/>
-      <c r="E127" s="4"/>
-    </row>
-    <row r="128" spans="2:5" ht="16.5">
-      <c r="B128" s="4"/>
-      <c r="C128" s="4"/>
-      <c r="D128" s="4"/>
-      <c r="E128" s="4"/>
-    </row>
-    <row r="129" spans="2:5" ht="16.5">
-      <c r="B129" s="4"/>
-      <c r="C129" s="4"/>
-      <c r="D129" s="4"/>
-      <c r="E129" s="4"/>
-    </row>
-    <row r="130" spans="2:5" ht="16.5">
-      <c r="B130" s="4"/>
-      <c r="C130" s="4"/>
-      <c r="D130" s="4"/>
-      <c r="E130" s="4"/>
-    </row>
-    <row r="131" spans="2:5" ht="16.5">
-      <c r="B131" s="4"/>
-      <c r="C131" s="4"/>
-      <c r="D131" s="4"/>
-      <c r="E131" s="4"/>
-    </row>
-    <row r="132" spans="2:5" ht="16.5">
-      <c r="B132" s="4"/>
-      <c r="C132" s="4"/>
-      <c r="D132" s="4"/>
-      <c r="E132" s="4"/>
-    </row>
-    <row r="133" spans="2:5" ht="16.5">
-      <c r="B133" s="4"/>
-      <c r="C133" s="4"/>
-      <c r="D133" s="4"/>
-      <c r="E133" s="4"/>
-    </row>
-    <row r="134" spans="2:5" ht="16.5">
-      <c r="B134" s="4"/>
-      <c r="C134" s="4"/>
-      <c r="D134" s="4"/>
-      <c r="E134" s="4"/>
-    </row>
-    <row r="135" spans="2:5" ht="16.5">
-      <c r="B135" s="4"/>
-      <c r="C135" s="4"/>
-      <c r="D135" s="4"/>
-      <c r="E135" s="4"/>
-    </row>
-    <row r="136" spans="2:5" ht="16.5">
-      <c r="B136" s="4"/>
-      <c r="C136" s="4"/>
-      <c r="D136" s="4"/>
-      <c r="E136" s="4"/>
-    </row>
-    <row r="137" spans="2:5" ht="16.5">
-      <c r="B137" s="4"/>
-      <c r="C137" s="4"/>
-      <c r="D137" s="4"/>
-      <c r="E137" s="4"/>
-    </row>
-    <row r="138" spans="2:5" ht="16.5">
-      <c r="B138" s="4"/>
-      <c r="C138" s="4"/>
-      <c r="D138" s="4"/>
-      <c r="E138" s="4"/>
-    </row>
-    <row r="139" spans="2:5" ht="16.5">
-      <c r="B139" s="4"/>
-      <c r="C139" s="4"/>
-      <c r="D139" s="4"/>
-      <c r="E139" s="4"/>
-    </row>
-    <row r="140" spans="2:5" ht="16.5">
-      <c r="B140" s="4"/>
-      <c r="C140" s="4"/>
-      <c r="D140" s="4"/>
-      <c r="E140" s="4"/>
-    </row>
-    <row r="141" spans="2:5" ht="16.5">
-      <c r="B141" s="4"/>
-      <c r="C141" s="4"/>
-      <c r="D141" s="4"/>
-      <c r="E141" s="4"/>
-    </row>
-    <row r="142" spans="2:5" ht="16.5">
-      <c r="B142" s="4"/>
-      <c r="C142" s="4"/>
-      <c r="D142" s="4"/>
-      <c r="E142" s="4"/>
-    </row>
-    <row r="143" spans="2:5" ht="16.5">
-      <c r="B143" s="4"/>
-      <c r="C143" s="4"/>
-      <c r="D143" s="4"/>
-      <c r="E143" s="4"/>
-    </row>
-    <row r="144" spans="2:5" ht="16.5">
-      <c r="B144" s="4"/>
-      <c r="C144" s="6"/>
-      <c r="D144" s="6"/>
-      <c r="E144" s="6"/>
-    </row>
-    <row r="145" spans="2:5" ht="16.5">
-      <c r="B145" s="4"/>
-      <c r="C145" s="6"/>
-      <c r="D145" s="6"/>
-      <c r="E145" s="6"/>
-    </row>
-    <row r="146" spans="2:5" ht="16.5">
-      <c r="B146" s="4"/>
-      <c r="C146" s="7"/>
-      <c r="D146" s="7"/>
-      <c r="E146" s="7"/>
-    </row>
-    <row r="147" spans="2:5">
-      <c r="B147" s="7"/>
-      <c r="C147" s="7"/>
-      <c r="D147" s="7"/>
-      <c r="E147" s="7"/>
-    </row>
-    <row r="148" spans="2:5">
-      <c r="B148" s="7"/>
-      <c r="C148" s="8"/>
-      <c r="D148" s="8"/>
-      <c r="E148" s="8"/>
-    </row>
-    <row r="149" spans="2:5">
-      <c r="B149" s="8"/>
+      <c r="H22" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J22" s="2">
+        <v>19</v>
+      </c>
+      <c r="P22" s="1">
+        <f>R22-Q22</f>
+        <v>710</v>
+      </c>
+      <c r="Q22" s="1">
+        <f>SUM(Q19:Q21)</f>
+        <v>4000</v>
+      </c>
+      <c r="R22" s="1">
+        <f>SUM(R15:R21)</f>
+        <v>4710</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="4:19" ht="16.5">
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+    </row>
+    <row r="24" spans="4:19" ht="16.5">
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+    </row>
+    <row r="25" spans="4:19" ht="16.5">
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+    </row>
+    <row r="26" spans="4:19" ht="16.5">
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+    </row>
+    <row r="27" spans="4:19" ht="16.5">
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+    </row>
+    <row r="28" spans="4:19" ht="16.5">
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+    </row>
+    <row r="29" spans="4:19" ht="16.5">
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+    </row>
+    <row r="30" spans="4:19" ht="16.5">
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+    </row>
+    <row r="31" spans="4:19" ht="16.5">
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+    </row>
+    <row r="32" spans="4:19" ht="16.5">
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+    </row>
+    <row r="33" spans="6:9" ht="16.5">
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+    </row>
+    <row r="34" spans="6:9" ht="16.5">
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+    </row>
+    <row r="35" spans="6:9" ht="16.5">
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+    </row>
+    <row r="36" spans="6:9" ht="16.5">
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+    </row>
+    <row r="37" spans="6:9" ht="16.5">
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+    </row>
+    <row r="38" spans="6:9" ht="16.5">
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+    </row>
+    <row r="39" spans="6:9" ht="16.5">
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+    </row>
+    <row r="40" spans="6:9" ht="16.5">
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+    </row>
+    <row r="41" spans="6:9" ht="16.5">
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+    </row>
+    <row r="42" spans="6:9" ht="16.5">
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+    </row>
+    <row r="43" spans="6:9" ht="16.5">
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+    </row>
+    <row r="44" spans="6:9" ht="16.5">
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+    </row>
+    <row r="45" spans="6:9" ht="16.5">
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+    </row>
+    <row r="46" spans="6:9" ht="16.5">
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+    </row>
+    <row r="47" spans="6:9" ht="16.5">
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+    </row>
+    <row r="48" spans="6:9" ht="16.5">
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+    </row>
+    <row r="49" spans="6:9" ht="16.5">
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+    </row>
+    <row r="50" spans="6:9" ht="16.5">
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+    </row>
+    <row r="51" spans="6:9" ht="16.5">
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+    </row>
+    <row r="52" spans="6:9" ht="16.5">
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+    </row>
+    <row r="53" spans="6:9" ht="16.5">
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+    </row>
+    <row r="54" spans="6:9" ht="16.5">
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+    </row>
+    <row r="55" spans="6:9" ht="16.5">
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+    </row>
+    <row r="56" spans="6:9" ht="16.5">
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+    </row>
+    <row r="57" spans="6:9" ht="16.5">
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+    </row>
+    <row r="58" spans="6:9" ht="16.5">
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+    </row>
+    <row r="59" spans="6:9" ht="16.5">
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+    </row>
+    <row r="60" spans="6:9" ht="16.5">
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+    </row>
+    <row r="61" spans="6:9" ht="16.5">
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+    </row>
+    <row r="62" spans="6:9" ht="16.5">
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+    </row>
+    <row r="63" spans="6:9" ht="16.5">
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+    </row>
+    <row r="64" spans="6:9" ht="16.5">
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+    </row>
+    <row r="65" spans="6:9" ht="16.5">
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+    </row>
+    <row r="66" spans="6:9" ht="16.5">
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+    </row>
+    <row r="67" spans="6:9" ht="16.5">
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+    </row>
+    <row r="68" spans="6:9" ht="16.5">
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+    </row>
+    <row r="69" spans="6:9" ht="16.5">
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+    </row>
+    <row r="70" spans="6:9" ht="16.5">
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+    </row>
+    <row r="71" spans="6:9" ht="16.5">
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+    </row>
+    <row r="72" spans="6:9" ht="16.5">
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+    </row>
+    <row r="73" spans="6:9" ht="16.5">
+      <c r="F73" s="4"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+      <c r="I73" s="4"/>
+    </row>
+    <row r="74" spans="6:9" ht="16.5">
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+    </row>
+    <row r="75" spans="6:9" ht="16.5">
+      <c r="F75" s="4"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
+    </row>
+    <row r="76" spans="6:9" ht="16.5">
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
+    </row>
+    <row r="77" spans="6:9" ht="16.5">
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
+    </row>
+    <row r="78" spans="6:9" ht="16.5">
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+    </row>
+    <row r="79" spans="6:9" ht="16.5">
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+    </row>
+    <row r="80" spans="6:9" ht="16.5">
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
+      <c r="I80" s="4"/>
+    </row>
+    <row r="81" spans="6:9" ht="16.5">
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+      <c r="I81" s="4"/>
+    </row>
+    <row r="82" spans="6:9" ht="16.5">
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+      <c r="I82" s="4"/>
+    </row>
+    <row r="83" spans="6:9" ht="16.5">
+      <c r="F83" s="4"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+      <c r="I83" s="4"/>
+    </row>
+    <row r="84" spans="6:9" ht="16.5">
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
+      <c r="I84" s="4"/>
+    </row>
+    <row r="85" spans="6:9" ht="16.5">
+      <c r="F85" s="4"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4"/>
+      <c r="I85" s="4"/>
+    </row>
+    <row r="86" spans="6:9" ht="16.5">
+      <c r="F86" s="4"/>
+      <c r="G86" s="4"/>
+      <c r="H86" s="4"/>
+      <c r="I86" s="4"/>
+    </row>
+    <row r="87" spans="6:9" ht="16.5">
+      <c r="F87" s="4"/>
+      <c r="G87" s="4"/>
+      <c r="H87" s="4"/>
+      <c r="I87" s="4"/>
+    </row>
+    <row r="88" spans="6:9" ht="16.5">
+      <c r="F88" s="4"/>
+      <c r="G88" s="4"/>
+      <c r="H88" s="4"/>
+      <c r="I88" s="4"/>
+    </row>
+    <row r="89" spans="6:9" ht="16.5">
+      <c r="F89" s="4"/>
+      <c r="G89" s="4"/>
+      <c r="H89" s="4"/>
+      <c r="I89" s="4"/>
+    </row>
+    <row r="90" spans="6:9" ht="16.5">
+      <c r="F90" s="4"/>
+      <c r="G90" s="4"/>
+      <c r="H90" s="4"/>
+      <c r="I90" s="4"/>
+    </row>
+    <row r="91" spans="6:9" ht="16.5">
+      <c r="F91" s="4"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="4"/>
+      <c r="I91" s="4"/>
+    </row>
+    <row r="92" spans="6:9" ht="16.5">
+      <c r="F92" s="4"/>
+      <c r="G92" s="4"/>
+      <c r="H92" s="4"/>
+      <c r="I92" s="4"/>
+    </row>
+    <row r="93" spans="6:9" ht="16.5">
+      <c r="F93" s="4"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="4"/>
+      <c r="I93" s="4"/>
+    </row>
+    <row r="94" spans="6:9" ht="16.5">
+      <c r="F94" s="4"/>
+      <c r="G94" s="4"/>
+      <c r="H94" s="4"/>
+      <c r="I94" s="4"/>
+    </row>
+    <row r="95" spans="6:9" ht="16.5">
+      <c r="F95" s="4"/>
+      <c r="G95" s="4"/>
+      <c r="H95" s="4"/>
+      <c r="I95" s="4"/>
+    </row>
+    <row r="96" spans="6:9" ht="16.5">
+      <c r="F96" s="4"/>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+      <c r="I96" s="4"/>
+    </row>
+    <row r="97" spans="6:9" ht="16.5">
+      <c r="F97" s="4"/>
+      <c r="G97" s="4"/>
+      <c r="H97" s="4"/>
+      <c r="I97" s="4"/>
+    </row>
+    <row r="98" spans="6:9" ht="16.5">
+      <c r="F98" s="4"/>
+      <c r="G98" s="4"/>
+      <c r="H98" s="4"/>
+      <c r="I98" s="4"/>
+    </row>
+    <row r="99" spans="6:9" ht="16.5">
+      <c r="F99" s="4"/>
+      <c r="G99" s="4"/>
+      <c r="H99" s="4"/>
+      <c r="I99" s="4"/>
+    </row>
+    <row r="100" spans="6:9" ht="16.5">
+      <c r="F100" s="4"/>
+      <c r="G100" s="4"/>
+      <c r="H100" s="4"/>
+      <c r="I100" s="4"/>
+    </row>
+    <row r="101" spans="6:9" ht="16.5">
+      <c r="F101" s="4"/>
+      <c r="G101" s="4"/>
+      <c r="H101" s="4"/>
+      <c r="I101" s="4"/>
+    </row>
+    <row r="102" spans="6:9" ht="16.5">
+      <c r="F102" s="4"/>
+      <c r="G102" s="4"/>
+      <c r="H102" s="4"/>
+      <c r="I102" s="4"/>
+    </row>
+    <row r="103" spans="6:9" ht="16.5">
+      <c r="F103" s="4"/>
+      <c r="G103" s="4"/>
+      <c r="H103" s="4"/>
+      <c r="I103" s="4"/>
+    </row>
+    <row r="104" spans="6:9" ht="16.5">
+      <c r="F104" s="4"/>
+      <c r="G104" s="4"/>
+      <c r="H104" s="4"/>
+      <c r="I104" s="4"/>
+    </row>
+    <row r="105" spans="6:9" ht="16.5">
+      <c r="F105" s="4"/>
+      <c r="G105" s="4"/>
+      <c r="H105" s="4"/>
+      <c r="I105" s="4"/>
+    </row>
+    <row r="106" spans="6:9" ht="16.5">
+      <c r="F106" s="4"/>
+      <c r="G106" s="4"/>
+      <c r="H106" s="4"/>
+      <c r="I106" s="4"/>
+    </row>
+    <row r="107" spans="6:9" ht="16.5">
+      <c r="F107" s="4"/>
+      <c r="G107" s="4"/>
+      <c r="H107" s="4"/>
+      <c r="I107" s="4"/>
+    </row>
+    <row r="108" spans="6:9" ht="16.5">
+      <c r="F108" s="4"/>
+      <c r="G108" s="4"/>
+      <c r="H108" s="4"/>
+      <c r="I108" s="4"/>
+    </row>
+    <row r="109" spans="6:9" ht="16.5">
+      <c r="F109" s="4"/>
+      <c r="G109" s="4"/>
+      <c r="H109" s="4"/>
+      <c r="I109" s="4"/>
+    </row>
+    <row r="110" spans="6:9" ht="16.5">
+      <c r="F110" s="4"/>
+      <c r="G110" s="4"/>
+      <c r="H110" s="4"/>
+      <c r="I110" s="4"/>
+    </row>
+    <row r="111" spans="6:9" ht="16.5">
+      <c r="F111" s="4"/>
+      <c r="G111" s="4"/>
+      <c r="H111" s="4"/>
+      <c r="I111" s="4"/>
+    </row>
+    <row r="112" spans="6:9" ht="16.5">
+      <c r="F112" s="4"/>
+      <c r="G112" s="4"/>
+      <c r="H112" s="4"/>
+      <c r="I112" s="4"/>
+    </row>
+    <row r="113" spans="6:9" ht="16.5">
+      <c r="F113" s="4"/>
+      <c r="G113" s="4"/>
+      <c r="H113" s="4"/>
+      <c r="I113" s="4"/>
+    </row>
+    <row r="114" spans="6:9" ht="16.5">
+      <c r="F114" s="4"/>
+      <c r="G114" s="4"/>
+      <c r="H114" s="4"/>
+      <c r="I114" s="4"/>
+    </row>
+    <row r="115" spans="6:9" ht="16.5">
+      <c r="F115" s="4"/>
+      <c r="G115" s="4"/>
+      <c r="H115" s="4"/>
+      <c r="I115" s="4"/>
+    </row>
+    <row r="116" spans="6:9" ht="16.5">
+      <c r="F116" s="4"/>
+      <c r="G116" s="4"/>
+      <c r="H116" s="4"/>
+      <c r="I116" s="4"/>
+    </row>
+    <row r="117" spans="6:9" ht="16.5">
+      <c r="F117" s="4"/>
+      <c r="G117" s="4"/>
+      <c r="H117" s="4"/>
+      <c r="I117" s="4"/>
+    </row>
+    <row r="118" spans="6:9" ht="16.5">
+      <c r="F118" s="4"/>
+      <c r="G118" s="4"/>
+      <c r="H118" s="4"/>
+      <c r="I118" s="4"/>
+    </row>
+    <row r="119" spans="6:9" ht="16.5">
+      <c r="F119" s="4"/>
+      <c r="G119" s="4"/>
+      <c r="H119" s="4"/>
+      <c r="I119" s="4"/>
+    </row>
+    <row r="120" spans="6:9" ht="16.5">
+      <c r="F120" s="4"/>
+      <c r="G120" s="4"/>
+      <c r="H120" s="4"/>
+      <c r="I120" s="4"/>
+    </row>
+    <row r="121" spans="6:9" ht="16.5">
+      <c r="F121" s="4"/>
+      <c r="G121" s="4"/>
+      <c r="H121" s="4"/>
+      <c r="I121" s="4"/>
+    </row>
+    <row r="122" spans="6:9" ht="16.5">
+      <c r="F122" s="4"/>
+      <c r="G122" s="4"/>
+      <c r="H122" s="4"/>
+      <c r="I122" s="4"/>
+    </row>
+    <row r="123" spans="6:9" ht="16.5">
+      <c r="F123" s="4"/>
+      <c r="G123" s="4"/>
+      <c r="H123" s="4"/>
+      <c r="I123" s="4"/>
+    </row>
+    <row r="124" spans="6:9" ht="16.5">
+      <c r="F124" s="4"/>
+      <c r="G124" s="4"/>
+      <c r="H124" s="4"/>
+      <c r="I124" s="4"/>
+    </row>
+    <row r="125" spans="6:9" ht="16.5">
+      <c r="F125" s="4"/>
+      <c r="G125" s="4"/>
+      <c r="H125" s="4"/>
+      <c r="I125" s="4"/>
+    </row>
+    <row r="126" spans="6:9" ht="16.5">
+      <c r="F126" s="4"/>
+      <c r="G126" s="4"/>
+      <c r="H126" s="4"/>
+      <c r="I126" s="4"/>
+    </row>
+    <row r="127" spans="6:9" ht="16.5">
+      <c r="F127" s="4"/>
+      <c r="G127" s="4"/>
+      <c r="H127" s="4"/>
+      <c r="I127" s="4"/>
+    </row>
+    <row r="128" spans="6:9" ht="16.5">
+      <c r="F128" s="4"/>
+      <c r="G128" s="4"/>
+      <c r="H128" s="4"/>
+      <c r="I128" s="4"/>
+    </row>
+    <row r="129" spans="6:9" ht="16.5">
+      <c r="F129" s="4"/>
+      <c r="G129" s="4"/>
+      <c r="H129" s="4"/>
+      <c r="I129" s="4"/>
+    </row>
+    <row r="130" spans="6:9" ht="16.5">
+      <c r="F130" s="4"/>
+      <c r="G130" s="4"/>
+      <c r="H130" s="4"/>
+      <c r="I130" s="4"/>
+    </row>
+    <row r="131" spans="6:9" ht="16.5">
+      <c r="F131" s="4"/>
+      <c r="G131" s="4"/>
+      <c r="H131" s="4"/>
+      <c r="I131" s="4"/>
+    </row>
+    <row r="132" spans="6:9" ht="16.5">
+      <c r="F132" s="4"/>
+      <c r="G132" s="4"/>
+      <c r="H132" s="4"/>
+      <c r="I132" s="4"/>
+    </row>
+    <row r="133" spans="6:9" ht="16.5">
+      <c r="F133" s="4"/>
+      <c r="G133" s="4"/>
+      <c r="H133" s="4"/>
+      <c r="I133" s="4"/>
+    </row>
+    <row r="134" spans="6:9" ht="16.5">
+      <c r="F134" s="4"/>
+      <c r="G134" s="4"/>
+      <c r="H134" s="4"/>
+      <c r="I134" s="4"/>
+    </row>
+    <row r="135" spans="6:9" ht="16.5">
+      <c r="F135" s="4"/>
+      <c r="G135" s="4"/>
+      <c r="H135" s="4"/>
+      <c r="I135" s="4"/>
+    </row>
+    <row r="136" spans="6:9" ht="16.5">
+      <c r="F136" s="4"/>
+      <c r="G136" s="4"/>
+      <c r="H136" s="4"/>
+      <c r="I136" s="4"/>
+    </row>
+    <row r="137" spans="6:9" ht="16.5">
+      <c r="F137" s="4"/>
+      <c r="G137" s="4"/>
+      <c r="H137" s="4"/>
+      <c r="I137" s="4"/>
+    </row>
+    <row r="138" spans="6:9" ht="16.5">
+      <c r="F138" s="4"/>
+      <c r="G138" s="4"/>
+      <c r="H138" s="4"/>
+      <c r="I138" s="4"/>
+    </row>
+    <row r="139" spans="6:9" ht="16.5">
+      <c r="F139" s="4"/>
+      <c r="G139" s="4"/>
+      <c r="H139" s="4"/>
+      <c r="I139" s="4"/>
+    </row>
+    <row r="140" spans="6:9" ht="16.5">
+      <c r="F140" s="4"/>
+      <c r="G140" s="4"/>
+      <c r="H140" s="4"/>
+      <c r="I140" s="4"/>
+    </row>
+    <row r="141" spans="6:9" ht="16.5">
+      <c r="F141" s="4"/>
+      <c r="G141" s="4"/>
+      <c r="H141" s="4"/>
+      <c r="I141" s="4"/>
+    </row>
+    <row r="142" spans="6:9" ht="16.5">
+      <c r="F142" s="4"/>
+      <c r="G142" s="6"/>
+      <c r="H142" s="6"/>
+      <c r="I142" s="6"/>
+    </row>
+    <row r="143" spans="6:9" ht="16.5">
+      <c r="F143" s="4"/>
+      <c r="G143" s="6"/>
+      <c r="H143" s="6"/>
+      <c r="I143" s="6"/>
+    </row>
+    <row r="144" spans="6:9" ht="16.5">
+      <c r="F144" s="4"/>
+      <c r="G144" s="7"/>
+      <c r="H144" s="7"/>
+      <c r="I144" s="7"/>
+    </row>
+    <row r="145" spans="6:9">
+      <c r="F145" s="7"/>
+      <c r="G145" s="7"/>
+      <c r="H145" s="7"/>
+      <c r="I145" s="7"/>
+    </row>
+    <row r="146" spans="6:9">
+      <c r="F146" s="7"/>
+      <c r="G146" s="8"/>
+      <c r="H146" s="8"/>
+      <c r="I146" s="8"/>
+    </row>
+    <row r="147" spans="6:9">
+      <c r="F147" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="D3:F4"/>
+    <mergeCell ref="H1:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2330,29 +2741,29 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:8" ht="15" customHeight="1">
-      <c r="C3" s="36">
+      <c r="C3" s="45">
         <v>2025</v>
       </c>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36">
+      <c r="D3" s="45"/>
+      <c r="E3" s="45">
         <f>SUM(Tableau24[المبلغ])</f>
         <v>2400</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="36" t="s">
+      <c r="G3" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="36"/>
+      <c r="H3" s="45"/>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1">
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
     </row>
     <row r="5" spans="2:8" ht="16.5">
       <c r="B5" s="3"/>
@@ -20158,7 +20569,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:S142"/>
+  <dimension ref="B2:Y142"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="1"/>
@@ -20170,652 +20581,1023 @@
     <col min="7" max="7" width="8" style="2" customWidth="1"/>
     <col min="8" max="9" width="11.42578125" style="1"/>
     <col min="10" max="10" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" style="1"/>
-    <col min="12" max="12" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.42578125" style="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="11.42578125" style="1"/>
+    <col min="18" max="18" width="22.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="23" width="11.42578125" style="1"/>
+    <col min="24" max="24" width="22.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:19">
+    <row r="2" spans="2:25">
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="2:19" ht="15" customHeight="1">
-      <c r="C3" s="38">
+    <row r="3" spans="2:25" ht="15" customHeight="1">
+      <c r="C3" s="48">
         <v>45962</v>
       </c>
-      <c r="D3" s="38"/>
-      <c r="E3" s="36">
+      <c r="D3" s="48"/>
+      <c r="E3" s="47">
         <f>SUM(E$6:E$1048576)</f>
-        <v>2100</v>
-      </c>
-      <c r="F3" s="36" t="s">
+        <v>2200</v>
+      </c>
+      <c r="F3" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="36"/>
-      <c r="I3" s="38">
+      <c r="G3" s="47"/>
+      <c r="I3" s="48">
         <v>45992</v>
       </c>
-      <c r="J3" s="38"/>
-      <c r="K3" s="36">
+      <c r="J3" s="48"/>
+      <c r="K3" s="47">
         <f>SUM(K$6:K$1048576)</f>
         <v>500</v>
       </c>
-      <c r="L3" s="36" t="s">
+      <c r="L3" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="36"/>
-      <c r="O3" s="38">
+      <c r="M3" s="47"/>
+      <c r="O3" s="48">
         <v>46023</v>
       </c>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="36">
+      <c r="P3" s="48"/>
+      <c r="Q3" s="47">
         <f>SUM(Q$6:Q$1048576)</f>
+        <v>650</v>
+      </c>
+      <c r="R3" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="S3" s="47"/>
+      <c r="U3" s="48">
+        <v>46054</v>
+      </c>
+      <c r="V3" s="48"/>
+      <c r="W3" s="47">
+        <f>SUM(W6:W23)</f>
+        <v>1460</v>
+      </c>
+      <c r="X3" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y3" s="47"/>
+    </row>
+    <row r="4" spans="2:25" ht="15" customHeight="1">
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="47"/>
+      <c r="R4" s="47"/>
+      <c r="S4" s="47"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="W4" s="47"/>
+      <c r="X4" s="47"/>
+      <c r="Y4" s="47"/>
+    </row>
+    <row r="5" spans="2:25">
+      <c r="B5" s="3"/>
+      <c r="C5" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="G5" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" s="41" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="L5" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="M5" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="O5" s="41" t="s">
+        <v>3</v>
+      </c>
+      <c r="P5" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q5" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="R5" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="S5" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="U5" s="41" t="s">
+        <v>3</v>
+      </c>
+      <c r="V5" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="W5" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="X5" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="40"/>
+    </row>
+    <row r="6" spans="2:25" ht="16.5" customHeight="1">
+      <c r="B6" s="3"/>
+      <c r="C6" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="36">
+        <v>45988</v>
+      </c>
+      <c r="E6" s="34">
+        <v>800</v>
+      </c>
+      <c r="F6" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="33"/>
+      <c r="I6" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="36">
+        <v>45994</v>
+      </c>
+      <c r="K6" s="35">
+        <v>50</v>
+      </c>
+      <c r="L6" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="M6" s="33">
+        <v>1</v>
+      </c>
+      <c r="O6" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" s="43">
+        <v>46025</v>
+      </c>
+      <c r="Q6" s="33">
+        <v>50</v>
+      </c>
+      <c r="R6" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="S6" s="33">
+        <v>1</v>
+      </c>
+      <c r="U6" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="V6" s="43">
+        <v>46055</v>
+      </c>
+      <c r="W6" s="33">
+        <v>50</v>
+      </c>
+      <c r="X6" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y6" s="33"/>
+    </row>
+    <row r="7" spans="2:25" ht="16.5" customHeight="1">
+      <c r="B7" s="9"/>
+      <c r="C7" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="36">
+        <v>45965</v>
+      </c>
+      <c r="E7" s="34">
+        <v>50</v>
+      </c>
+      <c r="F7" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="33">
+        <v>1</v>
+      </c>
+      <c r="I7" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" s="37">
+        <v>46013</v>
+      </c>
+      <c r="K7" s="34">
+        <v>50</v>
+      </c>
+      <c r="L7" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7" s="33">
+        <v>2</v>
+      </c>
+      <c r="O7" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="P7" s="43">
+        <v>46025</v>
+      </c>
+      <c r="Q7" s="34">
+        <v>50</v>
+      </c>
+      <c r="R7" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="S7" s="33">
+        <v>2</v>
+      </c>
+      <c r="U7" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="V7" s="43">
+        <v>46055</v>
+      </c>
+      <c r="W7" s="35">
+        <v>50</v>
+      </c>
+      <c r="X7" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y7" s="33"/>
+    </row>
+    <row r="8" spans="2:25" ht="20.25" customHeight="1">
+      <c r="B8" s="4"/>
+      <c r="C8" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="36">
+        <v>45965</v>
+      </c>
+      <c r="E8" s="34">
+        <v>50</v>
+      </c>
+      <c r="F8" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="33">
+        <v>2</v>
+      </c>
+      <c r="I8" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="37">
+        <v>46013</v>
+      </c>
+      <c r="K8" s="34">
+        <v>50</v>
+      </c>
+      <c r="L8" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="M8" s="33">
+        <v>3</v>
+      </c>
+      <c r="O8" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="P8" s="43">
+        <v>46048</v>
+      </c>
+      <c r="Q8" s="33">
+        <v>50</v>
+      </c>
+      <c r="R8" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="S8" s="33">
+        <v>3</v>
+      </c>
+      <c r="U8" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="V8" s="43">
+        <v>46056</v>
+      </c>
+      <c r="W8" s="35">
+        <v>50</v>
+      </c>
+      <c r="X8" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y8" s="33"/>
+    </row>
+    <row r="9" spans="2:25" ht="16.5" customHeight="1">
+      <c r="B9" s="4"/>
+      <c r="C9" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="36">
+        <v>45965</v>
+      </c>
+      <c r="E9" s="34">
+        <v>50</v>
+      </c>
+      <c r="F9" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="33">
+        <v>3</v>
+      </c>
+      <c r="I9" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="37">
+        <v>46021</v>
+      </c>
+      <c r="K9" s="33">
+        <v>50</v>
+      </c>
+      <c r="L9" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="M9" s="33">
+        <v>4</v>
+      </c>
+      <c r="O9" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="P9" s="43">
+        <v>46048</v>
+      </c>
+      <c r="Q9" s="33">
+        <v>200</v>
+      </c>
+      <c r="R9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="S9" s="33">
+        <v>4</v>
+      </c>
+      <c r="U9" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="V9" s="43">
+        <v>46056</v>
+      </c>
+      <c r="W9" s="35">
+        <v>50</v>
+      </c>
+      <c r="X9" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y9" s="33"/>
+    </row>
+    <row r="10" spans="2:25" ht="19.5" customHeight="1">
+      <c r="B10" s="4"/>
+      <c r="C10" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="36">
+        <v>45965</v>
+      </c>
+      <c r="E10" s="34">
+        <v>50</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="33">
+        <v>4</v>
+      </c>
+      <c r="I10" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="37">
+        <v>46021</v>
+      </c>
+      <c r="K10" s="33">
+        <v>50</v>
+      </c>
+      <c r="L10" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="M10" s="33">
+        <v>5</v>
+      </c>
+      <c r="O10" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="P10" s="43">
+        <v>46048</v>
+      </c>
+      <c r="Q10" s="33">
+        <v>50</v>
+      </c>
+      <c r="R10" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="S10" s="33">
+        <v>5</v>
+      </c>
+      <c r="U10" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="V10" s="43">
+        <v>46082</v>
+      </c>
+      <c r="W10" s="33">
+        <v>50</v>
+      </c>
+      <c r="X10" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y10" s="33"/>
+    </row>
+    <row r="11" spans="2:25" ht="16.5">
+      <c r="B11" s="4"/>
+      <c r="C11" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="36">
+        <v>45965</v>
+      </c>
+      <c r="E11" s="35">
+        <v>50</v>
+      </c>
+      <c r="F11" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="33">
+        <v>5</v>
+      </c>
+      <c r="I11" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" s="37">
+        <v>46022</v>
+      </c>
+      <c r="K11" s="33">
+        <v>50</v>
+      </c>
+      <c r="L11" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="M11" s="33">
+        <v>6</v>
+      </c>
+      <c r="O11" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="P11" s="43">
+        <v>46048</v>
+      </c>
+      <c r="Q11" s="34">
+        <v>50</v>
+      </c>
+      <c r="R11" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="S11" s="33">
+        <v>6</v>
+      </c>
+      <c r="U11" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="V11" s="43">
+        <v>46082</v>
+      </c>
+      <c r="W11" s="33">
         <v>100</v>
       </c>
-      <c r="R3" s="36" t="s">
-        <v>4</v>
-      </c>
-      <c r="S3" s="36"/>
-    </row>
-    <row r="4" spans="2:19" ht="15" customHeight="1">
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="36"/>
-      <c r="M4" s="36"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
-      <c r="S4" s="36"/>
-    </row>
-    <row r="5" spans="2:19" ht="16.5">
-      <c r="B5" s="3"/>
-      <c r="C5" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q5" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="R5" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:19" ht="16.5" customHeight="1">
-      <c r="B6" s="3"/>
-      <c r="C6" s="10" t="s">
+      <c r="X11" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y11" s="33"/>
+    </row>
+    <row r="12" spans="2:25" ht="16.5">
+      <c r="B12" s="4"/>
+      <c r="C12" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="36">
+        <v>45965</v>
+      </c>
+      <c r="E12" s="35">
+        <v>50</v>
+      </c>
+      <c r="F12" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="33">
+        <v>6</v>
+      </c>
+      <c r="I12" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" s="37">
+        <v>46023</v>
+      </c>
+      <c r="K12" s="33">
+        <v>50</v>
+      </c>
+      <c r="L12" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="M12" s="33">
+        <v>7</v>
+      </c>
+      <c r="O12" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="P12" s="43">
+        <v>46050</v>
+      </c>
+      <c r="Q12" s="33">
+        <v>100</v>
+      </c>
+      <c r="R12" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="S12" s="33">
+        <v>7</v>
+      </c>
+      <c r="U12" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="V12" s="43">
+        <v>46082</v>
+      </c>
+      <c r="W12" s="33">
+        <v>50</v>
+      </c>
+      <c r="X12" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y12" s="33"/>
+    </row>
+    <row r="13" spans="2:25" ht="16.5">
+      <c r="B13" s="4"/>
+      <c r="C13" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="36">
+        <v>45965</v>
+      </c>
+      <c r="E13" s="34">
+        <v>50</v>
+      </c>
+      <c r="F13" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="39">
+        <v>7</v>
+      </c>
+      <c r="I13" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="J13" s="37">
+        <v>46023</v>
+      </c>
+      <c r="K13" s="33">
+        <v>50</v>
+      </c>
+      <c r="L13" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="M13" s="33">
+        <v>8</v>
+      </c>
+      <c r="O13" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="P13" s="43">
+        <v>46051</v>
+      </c>
+      <c r="Q13" s="33">
+        <v>100</v>
+      </c>
+      <c r="R13" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="S13" s="33">
+        <v>8</v>
+      </c>
+      <c r="U13" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="V13" s="43">
+        <v>46082</v>
+      </c>
+      <c r="W13" s="33">
+        <v>100</v>
+      </c>
+      <c r="X13" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y13" s="33"/>
+    </row>
+    <row r="14" spans="2:25" ht="16.5">
+      <c r="B14" s="4"/>
+      <c r="C14" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="36">
+        <v>45965</v>
+      </c>
+      <c r="E14" s="35">
+        <v>100</v>
+      </c>
+      <c r="F14" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="39">
+        <v>8</v>
+      </c>
+      <c r="I14" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" s="37">
+        <v>46023</v>
+      </c>
+      <c r="K14" s="33">
+        <v>50</v>
+      </c>
+      <c r="L14" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="M14" s="33">
+        <v>9</v>
+      </c>
+      <c r="U14" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="V14" s="43">
+        <v>46082</v>
+      </c>
+      <c r="W14" s="33">
+        <v>100</v>
+      </c>
+      <c r="X14" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y14" s="33" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="2:25" ht="16.5">
+      <c r="B15" s="4"/>
+      <c r="C15" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="36">
+        <v>45965</v>
+      </c>
+      <c r="E15" s="35">
+        <v>100</v>
+      </c>
+      <c r="F15" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="39">
+        <v>9</v>
+      </c>
+      <c r="I15" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="J15" s="37">
+        <v>46023</v>
+      </c>
+      <c r="K15" s="33">
+        <v>50</v>
+      </c>
+      <c r="L15" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="M15" s="33">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="30"/>
+      <c r="U15" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="V15" s="43">
+        <v>46082</v>
+      </c>
+      <c r="W15" s="33">
+        <v>50</v>
+      </c>
+      <c r="X15" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y15" s="33"/>
+    </row>
+    <row r="16" spans="2:25" ht="16.5">
+      <c r="B16" s="4"/>
+      <c r="C16" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="36">
+        <v>45965</v>
+      </c>
+      <c r="E16" s="35">
+        <v>100</v>
+      </c>
+      <c r="F16" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="39">
+        <v>10</v>
+      </c>
+      <c r="U16" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="V16" s="43">
+        <v>46082</v>
+      </c>
+      <c r="W16" s="33">
+        <v>100</v>
+      </c>
+      <c r="X16" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y16" s="33" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="2:25" ht="16.5">
+      <c r="B17" s="4"/>
+      <c r="C17" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="36">
+        <v>45965</v>
+      </c>
+      <c r="E17" s="35">
+        <v>50</v>
+      </c>
+      <c r="F17" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="39">
+        <v>11</v>
+      </c>
+      <c r="U17" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="V17" s="43">
+        <v>46082</v>
+      </c>
+      <c r="W17" s="33">
+        <v>100</v>
+      </c>
+      <c r="X17" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y17" s="33"/>
+    </row>
+    <row r="18" spans="2:25" ht="16.5">
+      <c r="B18" s="4"/>
+      <c r="C18" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="36">
+        <v>45965</v>
+      </c>
+      <c r="E18" s="35">
+        <v>50</v>
+      </c>
+      <c r="F18" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="39">
+        <v>12</v>
+      </c>
+      <c r="U18" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="V18" s="43">
+        <v>46082</v>
+      </c>
+      <c r="W18" s="33">
+        <v>50</v>
+      </c>
+      <c r="X18" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y18" s="33" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" ht="16.5">
+      <c r="B19" s="4"/>
+      <c r="C19" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="36">
+        <v>45965</v>
+      </c>
+      <c r="E19" s="35">
+        <v>50</v>
+      </c>
+      <c r="F19" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="G19" s="39">
+        <v>13</v>
+      </c>
+      <c r="U19" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="V19" s="43">
+        <v>46082</v>
+      </c>
+      <c r="W19" s="33">
+        <v>300</v>
+      </c>
+      <c r="X19" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y19" s="33" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" ht="17.25" customHeight="1">
+      <c r="B20" s="4"/>
+      <c r="C20" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D20" s="36">
         <v>45988</v>
       </c>
-      <c r="E6" s="4">
-        <v>800</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="I6" s="10" t="s">
+      <c r="E20" s="35">
+        <v>200</v>
+      </c>
+      <c r="F20" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" s="39">
+        <v>14</v>
+      </c>
+      <c r="U20" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="V20" s="43">
+        <v>46082</v>
+      </c>
+      <c r="W20" s="33">
+        <v>50</v>
+      </c>
+      <c r="X20" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y20" s="33"/>
+    </row>
+    <row r="21" spans="2:25" ht="16.5">
+      <c r="B21" s="4"/>
+      <c r="C21" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="11">
-        <v>45994</v>
-      </c>
-      <c r="K6" s="10">
+      <c r="D21" s="36">
+        <v>45990</v>
+      </c>
+      <c r="E21" s="35">
         <v>50</v>
       </c>
-      <c r="L6" s="10" t="s">
+      <c r="F21" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" s="39">
+        <v>15</v>
+      </c>
+      <c r="U21" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="V21" s="43">
+        <v>46083</v>
+      </c>
+      <c r="W21" s="33">
+        <v>100</v>
+      </c>
+      <c r="X21" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="M6" s="1">
-        <v>1</v>
-      </c>
-      <c r="O6" s="4" t="s">
+      <c r="Y21" s="33"/>
+    </row>
+    <row r="22" spans="2:25" ht="16.5">
+      <c r="B22" s="4"/>
+      <c r="C22" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="P6" s="15">
-        <v>46025</v>
-      </c>
-      <c r="Q6" s="1">
+      <c r="D22" s="36">
+        <v>45990</v>
+      </c>
+      <c r="E22" s="35">
         <v>50</v>
       </c>
-      <c r="R6" s="10" t="s">
+      <c r="F22" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" s="39">
+        <v>16</v>
+      </c>
+      <c r="U22" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="V22" s="43">
+        <v>46084</v>
+      </c>
+      <c r="W22" s="33">
+        <v>60</v>
+      </c>
+      <c r="X22" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y22" s="33" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="2:25" ht="16.5">
+      <c r="B23" s="4"/>
+      <c r="C23" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="36">
+        <v>45990</v>
+      </c>
+      <c r="E23" s="35">
+        <v>50</v>
+      </c>
+      <c r="F23" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="G23" s="39">
+        <v>17</v>
+      </c>
+      <c r="U23" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="V23" s="43">
+        <v>46087</v>
+      </c>
+      <c r="W23" s="33">
+        <v>50</v>
+      </c>
+      <c r="X23" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y23" s="33" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="2:25" ht="16.5">
+      <c r="B24" s="4"/>
+      <c r="C24" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="36">
+        <v>45990</v>
+      </c>
+      <c r="E24" s="35">
+        <v>100</v>
+      </c>
+      <c r="F24" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="G24" s="39">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="2:25" s="2" customFormat="1" ht="16.5">
+      <c r="B25" s="4"/>
+      <c r="C25" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" s="36">
+        <v>45991</v>
+      </c>
+      <c r="E25" s="35">
+        <v>50</v>
+      </c>
+      <c r="F25" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="2:19" ht="16.5" customHeight="1">
-      <c r="B7" s="9"/>
-      <c r="C7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="11">
-        <v>45965</v>
-      </c>
-      <c r="E7" s="4">
-        <v>50</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J7" s="16">
-        <v>46013</v>
-      </c>
-      <c r="K7" s="4">
-        <v>50</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" s="1">
-        <v>2</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="P7" s="15">
-        <v>46025</v>
-      </c>
-      <c r="Q7" s="27">
-        <v>50</v>
-      </c>
-      <c r="R7" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="S7" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="2:19" ht="20.25" customHeight="1">
-      <c r="B8" s="4"/>
-      <c r="C8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="11">
-        <v>45965</v>
-      </c>
-      <c r="E8" s="4">
-        <v>50</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="1">
-        <v>2</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" s="16">
-        <v>46013</v>
-      </c>
-      <c r="K8" s="4">
-        <v>50</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="M8" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="2:19" ht="16.5" customHeight="1">
-      <c r="B9" s="4"/>
-      <c r="C9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="11">
-        <v>45965</v>
-      </c>
-      <c r="E9" s="4">
-        <v>50</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="1">
-        <v>3</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J9" s="16">
-        <v>46021</v>
-      </c>
-      <c r="K9" s="1">
-        <v>50</v>
-      </c>
-      <c r="L9" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="M9" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="2:19" ht="16.5">
-      <c r="B10" s="4"/>
-      <c r="C10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="11">
-        <v>45965</v>
-      </c>
-      <c r="E10" s="4">
-        <v>50</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="1">
-        <v>4</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" s="16">
-        <v>46021</v>
-      </c>
-      <c r="K10" s="1">
-        <v>50</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="M10" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="2:19" ht="16.5">
-      <c r="B11" s="4"/>
-      <c r="C11" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="11">
-        <v>45965</v>
-      </c>
-      <c r="E11" s="10">
-        <v>50</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="1">
-        <v>5</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J11" s="16">
-        <v>46022</v>
-      </c>
-      <c r="K11" s="1">
-        <v>50</v>
-      </c>
-      <c r="L11" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="M11" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="2:19" ht="16.5">
-      <c r="B12" s="4"/>
-      <c r="C12" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="11">
-        <v>45965</v>
-      </c>
-      <c r="E12" s="10">
-        <v>50</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" s="1">
-        <v>6</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J12" s="16">
-        <v>46023</v>
-      </c>
-      <c r="K12" s="1">
-        <v>50</v>
-      </c>
-      <c r="L12" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="M12" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="2:19" ht="16.5">
-      <c r="B13" s="4"/>
-      <c r="C13" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="11">
-        <v>45965</v>
-      </c>
-      <c r="E13" s="4">
-        <v>50</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13" s="2">
-        <v>7</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J13" s="16">
-        <v>46023</v>
-      </c>
-      <c r="K13" s="1">
-        <v>50</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="M13" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="2:19" ht="16.5">
-      <c r="B14" s="4"/>
-      <c r="C14" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="11">
-        <v>45965</v>
-      </c>
-      <c r="E14" s="10">
-        <v>100</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" s="2">
-        <v>8</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J14" s="16">
-        <v>46023</v>
-      </c>
-      <c r="K14" s="1">
-        <v>50</v>
-      </c>
-      <c r="L14" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="M14" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="2:19" ht="16.5">
-      <c r="B15" s="4"/>
-      <c r="C15" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="11">
-        <v>45965</v>
-      </c>
-      <c r="E15" s="10">
-        <v>100</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="2">
-        <v>9</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J15" s="16">
-        <v>46023</v>
-      </c>
-      <c r="K15" s="1">
-        <v>50</v>
-      </c>
-      <c r="L15" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="M15" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="2:19" ht="16.5">
-      <c r="B16" s="4"/>
-      <c r="C16" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="11">
-        <v>45965</v>
-      </c>
-      <c r="E16" s="10">
-        <v>100</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13" ht="16.5">
-      <c r="B17" s="4"/>
-      <c r="C17" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="11">
-        <v>45965</v>
-      </c>
-      <c r="E17" s="10">
-        <v>50</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13" ht="16.5">
-      <c r="B18" s="4"/>
-      <c r="C18" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" s="11">
-        <v>45965</v>
-      </c>
-      <c r="E18" s="10">
-        <v>50</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="G18" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="2:13" ht="16.5">
-      <c r="B19" s="4"/>
-      <c r="C19" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="11">
-        <v>45965</v>
-      </c>
-      <c r="E19" s="10">
-        <v>50</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G19" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B20" s="4"/>
-      <c r="C20" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" s="11">
-        <v>45988</v>
-      </c>
-      <c r="E20" s="10">
-        <v>200</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G20" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="2:13" ht="16.5">
-      <c r="B21" s="4"/>
-      <c r="C21" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="11">
-        <v>45990</v>
-      </c>
-      <c r="E21" s="10">
-        <v>50</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G21" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="2:13" ht="16.5">
-      <c r="B22" s="4"/>
-      <c r="C22" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" s="11">
-        <v>45990</v>
-      </c>
-      <c r="E22" s="10">
-        <v>50</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="2:13" ht="16.5">
-      <c r="B23" s="4"/>
-      <c r="C23" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="11">
-        <v>45990</v>
-      </c>
-      <c r="E23" s="10">
-        <v>50</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G23" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="2:13" ht="16.5">
-      <c r="B24" s="4"/>
-      <c r="C24" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="11">
-        <v>45990</v>
-      </c>
-      <c r="E24" s="10">
-        <v>100</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G24" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13" s="2" customFormat="1" ht="16.5">
-      <c r="B25" s="4"/>
-      <c r="C25" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D25" s="11">
-        <v>45991</v>
-      </c>
-      <c r="E25" s="10">
-        <v>50</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G25" s="2">
+      <c r="G25" s="39">
         <v>19</v>
       </c>
       <c r="I25" s="1"/>
@@ -20823,62 +21605,96 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
-    </row>
-    <row r="26" spans="2:13" s="2" customFormat="1" ht="16.5">
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1"/>
+      <c r="W25" s="1"/>
+      <c r="X25" s="1"/>
+      <c r="Y25" s="1"/>
+    </row>
+    <row r="26" spans="2:25" s="2" customFormat="1" ht="16.5">
       <c r="B26" s="4"/>
       <c r="C26" s="10"/>
       <c r="D26" s="14"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
     </row>
-    <row r="27" spans="2:13" s="2" customFormat="1" ht="16.5">
+    <row r="27" spans="2:25" s="2" customFormat="1" ht="16.5">
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
       <c r="D27" s="5"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
     </row>
-    <row r="28" spans="2:13" s="2" customFormat="1" ht="16.5">
+    <row r="28" spans="2:25" s="2" customFormat="1" ht="16.5">
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="5"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" spans="2:13" s="2" customFormat="1" ht="16.5">
+    <row r="29" spans="2:25" s="2" customFormat="1" ht="16.5">
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
       <c r="D29" s="5"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" spans="2:13" s="2" customFormat="1" ht="16.5">
+    <row r="30" spans="2:25" s="2" customFormat="1" ht="16.5">
       <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-    </row>
-    <row r="31" spans="2:13" s="2" customFormat="1" ht="16.5">
+      <c r="C30" s="48">
+        <v>46082</v>
+      </c>
+      <c r="D30" s="48"/>
+      <c r="E30" s="47">
+        <f>SUM(E33:E50)</f>
+        <v>50</v>
+      </c>
+      <c r="F30" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="G30" s="47"/>
+    </row>
+    <row r="31" spans="2:25" s="2" customFormat="1" ht="16.5">
       <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-    </row>
-    <row r="32" spans="2:13" s="2" customFormat="1" ht="16.5">
+      <c r="C31" s="48"/>
+      <c r="D31" s="48"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="47"/>
+      <c r="G31" s="47"/>
+    </row>
+    <row r="32" spans="2:25" s="2" customFormat="1" ht="16.5">
       <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
+      <c r="C32" s="41" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="F32" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="G32" s="40" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="33" spans="2:6" s="2" customFormat="1" ht="16.5">
       <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
+      <c r="C33" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="16">
+        <v>46088</v>
+      </c>
+      <c r="E33" s="4">
+        <v>50</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="34" spans="2:6" s="2" customFormat="1" ht="16.5">
       <c r="B34" s="4"/>
@@ -21545,111 +22361,123 @@
       <c r="E128" s="4"/>
       <c r="F128" s="4"/>
     </row>
-    <row r="129" spans="2:13" s="2" customFormat="1" ht="16.5">
+    <row r="129" spans="2:25" s="2" customFormat="1" ht="16.5">
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
       <c r="D129" s="5"/>
       <c r="E129" s="4"/>
       <c r="F129" s="4"/>
     </row>
-    <row r="130" spans="2:13" s="2" customFormat="1" ht="16.5">
+    <row r="130" spans="2:25" s="2" customFormat="1" ht="16.5">
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
       <c r="D130" s="5"/>
       <c r="E130" s="4"/>
       <c r="F130" s="4"/>
     </row>
-    <row r="131" spans="2:13" s="2" customFormat="1" ht="16.5">
+    <row r="131" spans="2:25" s="2" customFormat="1" ht="16.5">
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
       <c r="D131" s="5"/>
       <c r="E131" s="4"/>
       <c r="F131" s="4"/>
     </row>
-    <row r="132" spans="2:13" s="2" customFormat="1" ht="16.5">
+    <row r="132" spans="2:25" s="2" customFormat="1" ht="16.5">
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
       <c r="D132" s="5"/>
       <c r="E132" s="4"/>
       <c r="F132" s="4"/>
     </row>
-    <row r="133" spans="2:13" s="2" customFormat="1" ht="16.5">
+    <row r="133" spans="2:25" s="2" customFormat="1" ht="16.5">
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
       <c r="D133" s="5"/>
       <c r="E133" s="4"/>
       <c r="F133" s="4"/>
     </row>
-    <row r="134" spans="2:13" s="2" customFormat="1" ht="16.5">
+    <row r="134" spans="2:25" s="2" customFormat="1" ht="16.5">
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
       <c r="D134" s="5"/>
       <c r="E134" s="4"/>
       <c r="F134" s="4"/>
     </row>
-    <row r="135" spans="2:13" s="2" customFormat="1" ht="16.5">
+    <row r="135" spans="2:25" s="2" customFormat="1" ht="16.5">
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
       <c r="D135" s="5"/>
       <c r="E135" s="4"/>
       <c r="F135" s="4"/>
     </row>
-    <row r="136" spans="2:13" s="2" customFormat="1" ht="16.5">
+    <row r="136" spans="2:25" s="2" customFormat="1" ht="16.5">
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
       <c r="D136" s="6"/>
       <c r="E136" s="6"/>
       <c r="F136" s="6"/>
     </row>
-    <row r="137" spans="2:13" s="2" customFormat="1" ht="16.5">
+    <row r="137" spans="2:25" s="2" customFormat="1" ht="16.5">
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
       <c r="D137" s="6"/>
       <c r="E137" s="6"/>
       <c r="F137" s="6"/>
     </row>
-    <row r="138" spans="2:13" s="2" customFormat="1" ht="16.5">
+    <row r="138" spans="2:25" s="2" customFormat="1" ht="16.5">
       <c r="B138" s="4"/>
       <c r="C138" s="7"/>
       <c r="D138" s="7"/>
       <c r="E138" s="7"/>
       <c r="F138" s="7"/>
     </row>
-    <row r="139" spans="2:13" s="2" customFormat="1">
+    <row r="139" spans="2:25" s="2" customFormat="1">
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
       <c r="D139" s="7"/>
       <c r="E139" s="7"/>
       <c r="F139" s="7"/>
     </row>
-    <row r="140" spans="2:13" s="2" customFormat="1">
+    <row r="140" spans="2:25" s="2" customFormat="1">
       <c r="B140" s="7"/>
       <c r="C140" s="8"/>
       <c r="D140" s="8"/>
       <c r="E140" s="8"/>
       <c r="F140" s="8"/>
     </row>
-    <row r="141" spans="2:13" s="2" customFormat="1">
+    <row r="141" spans="2:25" s="2" customFormat="1">
       <c r="B141" s="8"/>
     </row>
-    <row r="142" spans="2:13">
+    <row r="142" spans="2:25">
       <c r="I142" s="2"/>
       <c r="J142" s="2"/>
       <c r="K142" s="2"/>
       <c r="L142" s="2"/>
       <c r="M142" s="2"/>
+      <c r="T142" s="2"/>
+      <c r="U142" s="2"/>
+      <c r="V142" s="2"/>
+      <c r="W142" s="2"/>
+      <c r="X142" s="2"/>
+      <c r="Y142" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="O3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:S4"/>
+  <mergeCells count="15">
+    <mergeCell ref="C30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:G31"/>
     <mergeCell ref="C3:D4"/>
     <mergeCell ref="I3:J4"/>
     <mergeCell ref="L3:M4"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="F3:G4"/>
     <mergeCell ref="E3:E4"/>
+    <mergeCell ref="U3:V4"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="X3:Y4"/>
+    <mergeCell ref="O3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:S4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
